--- a/Employee_Reports_wi48/Trevin Christopher Neydorf Q0531.xlsx
+++ b/Employee_Reports_wi48/Trevin Christopher Neydorf Q0531.xlsx
@@ -454,13 +454,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="73" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -667,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -716,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -765,11 +765,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -814,11 +814,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -863,11 +863,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -961,11 +961,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1010,11 +1010,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1059,11 +1059,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1108,11 +1108,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1157,11 +1157,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1206,11 +1206,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1255,11 +1255,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1304,11 +1304,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1353,11 +1353,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1402,11 +1402,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1452,11 +1452,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1501,11 +1501,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1550,11 +1550,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1573,9 +1573,21 @@
           <t>Procedure For Handling New or Unfamilliar Task (SOPs)</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr"/>
-      <c r="D24" s="3" t="inlineStr"/>
-      <c r="E24" s="3" t="inlineStr"/>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>LSME-IMS-SOP-022</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
           <t>06-Jun-2026</t>
@@ -1587,11 +1599,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1636,11 +1648,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1656,36 +1668,85 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
+          <t>Matar LOTO Procedure (SOPs)</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>MATAR</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>FM-DE-24-SOP-SA-013</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>01-Jul-2026</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>01-Jul-2027</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>350</v>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
           <t>IS0 55001 (Other Trainings)</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr"/>
-      <c r="D26" s="3" t="inlineStr"/>
-      <c r="E26" s="3" t="inlineStr"/>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr"/>
+      <c r="D27" s="3" t="inlineStr"/>
+      <c r="E27" s="3" t="inlineStr"/>
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>01-Jul-2025</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>01-Jul-2027</t>
         </is>
       </c>
-      <c r="H26" s="3" t="n">
-        <v>353</v>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="n">
+        <v>350</v>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2224,7 +2285,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7945</v>
+        <v>7942</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2247,7 +2308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2319,7 +2380,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7933</v>
+        <v>7930</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2348,7 +2409,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7933</v>
+        <v>7930</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2377,7 +2438,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7936</v>
+        <v>7933</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2406,7 +2467,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7965</v>
+        <v>7962</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2435,7 +2496,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7965</v>
+        <v>7962</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -2464,7 +2525,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7936</v>
+        <v>7933</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -2493,7 +2554,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7965</v>
+        <v>7962</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -2522,7 +2583,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7965</v>
+        <v>7962</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -2551,7 +2612,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7979</v>
+        <v>7976</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -2580,7 +2641,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7965</v>
+        <v>7962</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -2595,21 +2656,21 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>fmc deck</t>
+          <t>uldtv 20ft</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>07-Jul-2026</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>17-May-2048</t>
+          <t>01-Jun-2048</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7979</v>
+        <v>7991</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -2624,21 +2685,21 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>powered roller deckmatarsop</t>
+          <t>uldtv 15ft</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>07-Jul-2026</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>17-May-2048</t>
+          <t>01-Jun-2048</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7979</v>
+        <v>7991</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -2653,21 +2714,21 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>non powered roller deckmatarsop</t>
+          <t>bbtv 20ft</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>07-Jul-2026</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>17-May-2048</t>
+          <t>01-Jun-2048</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7979</v>
+        <v>7991</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -2682,28 +2743,173 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
+          <t>bbtv 15ft</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>07-Jul-2026</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>01-Jun-2048</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>7991</v>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>fmc deck</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>22-Jun-2026</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>17-May-2048</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>7976</v>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>powered roller deckmatarsop</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>22-Jun-2026</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>17-May-2048</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>7976</v>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>non powered roller deckmatarsop</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>22-Jun-2026</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>17-May-2048</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>7976</v>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
           <t>ball deck</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>22-Jun-2026</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>17-May-2048</t>
         </is>
       </c>
-      <c r="E16" s="3" t="n">
-        <v>7979</v>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="n"/>
+      <c r="E20" s="3" t="n">
+        <v>7976</v>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>floor scale</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>07-Jul-2026</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>01-Jun-2048</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>7991</v>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
